--- a/dados/excel/quadro_tempo_servico_por_ano.xlsx
+++ b/dados/excel/quadro_tempo_servico_por_ano.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -1441,16 +1441,16 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>40401</v>
+        <v>46388</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>5987</v>
+        <v>6456</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>227157226.13</v>
+        <v>261088150.26</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5622.564444691963</v>
+        <v>5628.355399241183</v>
       </c>
     </row>
     <row r="31">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>16803</v>
+        <v>18979</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>2121</v>
+        <v>2350</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>109964344.59</v>
+        <v>125980057.32</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>6544.328071772898</v>
+        <v>6637.865921281416</v>
       </c>
     </row>
     <row r="32">
@@ -1485,16 +1485,16 @@
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>31063</v>
+        <v>34571</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>3592</v>
+        <v>3675</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>255933944.1</v>
+        <v>288587929.01</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>8239.189521295431</v>
+        <v>8347.688207167857</v>
       </c>
     </row>
     <row r="33">
@@ -1507,16 +1507,16 @@
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>17913</v>
+        <v>19945</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>1966</v>
+        <v>1983</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>198528757.29</v>
+        <v>223833954.74</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>11082.94296265282</v>
+        <v>11222.55977638506</v>
       </c>
     </row>
     <row r="34">
@@ -1529,16 +1529,16 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>7085</v>
+        <v>7892</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>839</v>
+        <v>855</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>84326103.37</v>
+        <v>94679702.34999999</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>11902.06116725476</v>
+        <v>11996.92123035986</v>
       </c>
     </row>
     <row r="35">
@@ -1551,16 +1551,16 @@
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>1667</v>
+        <v>1864</v>
       </c>
       <c r="D35" s="11" t="n">
         <v>194</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>23738119.24</v>
+        <v>26772156.4</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>14240.02353929214</v>
+        <v>14362.74484978541</v>
       </c>
     </row>
     <row r="36">
@@ -1573,16 +1573,16 @@
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>7519</v>
+        <v>8067</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>1414</v>
+        <v>1520</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>78965378.91</v>
+        <v>87643143.37</v>
       </c>
       <c r="F36" s="10" t="n">
-        <v>10502.11183801037</v>
+        <v>10864.40354158919</v>
       </c>
     </row>
   </sheetData>
